--- a/AAII_Financials/Quarterly/CM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
   <si>
     <t>CM</t>
   </si>
@@ -656,271 +656,277 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E7" s="2">
         <v>46142</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45961</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45869</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45777</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45688</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45596</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45504</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45412</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45322</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45230</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45138</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45046</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44957</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44865</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44773</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44592</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44500</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44316</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44227</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44043</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43951</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43861</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43769</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43677</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43585</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43496</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43404</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43312</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43220</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43131</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43039</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42947</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42855</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42766</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5562900</v>
+      </c>
+      <c r="E8" s="3">
         <v>5437000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5772600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4974400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4837600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4643900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4634800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4447800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4431200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4110900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4212600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3820300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3889300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3883200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7552500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5970000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4286100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3086900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2865100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2766700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2711100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2682800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2831500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2913200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2942400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3691300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4068100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4114300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4369900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3868300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3944600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3441600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3429700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3183500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2964900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2846600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2543700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2426100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2452200</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2393000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1041,53 +1047,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5562900</v>
+      </c>
+      <c r="E10" s="3">
         <v>5437000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5772600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4974400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4837600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4643900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4634800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4447800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4431200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4110900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4212600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3820300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3889300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3883200</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1163,8 +1172,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,8 +1467,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1486,17 +1505,17 @@
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3">
         <v>4300</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1573,53 +1592,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>221900</v>
+        <v>316500</v>
       </c>
       <c r="E15" s="3">
         <v>221900</v>
       </c>
       <c r="F15" s="3">
+        <v>221900</v>
+      </c>
+      <c r="G15" s="3">
         <v>52400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>207400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>203400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>197600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>207400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>229500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>209500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>206300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>223200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>208300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>207900</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3339600</v>
+      </c>
+      <c r="E17" s="3">
         <v>3084700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3191500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2982100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2872900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2763700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2679500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2720500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2665500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2547300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2589900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2472500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2514000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2315400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5410400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3966600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2074300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1062200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>642700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>618200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>494800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>644200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>810200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>995900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1252700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2631500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2105500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2243900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2377700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2170900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2206300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1788400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1671200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1479200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1238400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1183300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1005400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>954100</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>969500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>942600</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2223300</v>
+      </c>
+      <c r="E18" s="3">
         <v>2352300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2581100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1992300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1964700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1880100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1955400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1727300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1765700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1563600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1622700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1347800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1375200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1567700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2142100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2003400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2211800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2024700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2222500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2148500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2216300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2038600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>2021300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1917400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1689700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1059800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1962600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1870400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1992200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1697500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1738300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1653200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1758500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1704300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1726600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1663300</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1538300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1471900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1482700</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1450400</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,8 +2056,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2068,208 +2101,214 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-1279400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-932800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-626700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-600500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-477600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-778100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-559300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-428700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-452000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-830300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-554300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-697100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-762300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-676000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-524000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-389500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-608900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-492700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-453200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-464500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-440600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-569300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-464400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-516300</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-159000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-596100</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2539800</v>
+      </c>
+      <c r="E21" s="3">
         <v>2574200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2803000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2044800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2172000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2083500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2153000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1934700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1995200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1773100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1829000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1571100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1583500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1775700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1066600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1273100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1777300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1610300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1928800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1582900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1837800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1796800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1747300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1329400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1326300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>560500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1393500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1437700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1615000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1445000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1261000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1278200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1431100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1361800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1409500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1207100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1180300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1053200</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1415800</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>953400</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2312,8 +2351,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2390,252 +2429,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2223300</v>
+      </c>
+      <c r="E23" s="3">
         <v>2352300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2581100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1992300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1964700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1880100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1955400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1727300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1765700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1563600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1622700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1343500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1375200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1567700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>862700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1070500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1585100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1424200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1744800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1370400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1657000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1609800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1569300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1087100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1135400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>362700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1200300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1194500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1468200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1307900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1129300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1160500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1305300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1239800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1286000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1094000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1073900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>955700</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1323700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>854300</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>506100</v>
+      </c>
+      <c r="E24" s="3">
         <v>541400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>295600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>436700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>450200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>427700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>455300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>376700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>466200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>291000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>331100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>274300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>286600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>322200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>544000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>207000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>354000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>317000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>386000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>304300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>375600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>370200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>349100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>308200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>236900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>55000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>248900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>264300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>309200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>270200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>219400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>239100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>274800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>246900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>232200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>227700</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>257500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>149000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>242800</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>139000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1717200</v>
+      </c>
+      <c r="E26" s="3">
         <v>1810900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2285400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1555600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1514500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1452400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1500000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1350600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1299500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1272600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1291600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1069200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1088600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1245500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>318700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>863600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1231200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1107200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1358800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1066100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1281500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1239700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1220100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>778900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>898500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>307700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>951500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>930100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1159000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1037700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>909900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>921400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1030600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>992900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1053800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>866300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>816400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>806600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1080900</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>715200</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1618800</v>
+      </c>
+      <c r="E27" s="3">
         <v>1721300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2202100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1468600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1453800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1389500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1433700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1293100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1247300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1220900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1232500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1018800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1030900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1188000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>259100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>831500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1192700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1069400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1325300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1028400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1255600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1198400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1194600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>755100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>873200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>290500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>921600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>899000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1130800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1010800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>889100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>902500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1010200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>970300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1036700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>844700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>806700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>795100</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1070100</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>704500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3208,8 +3268,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
@@ -3226,12 +3286,12 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-65500</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,8 +3554,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3532,208 +3601,214 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>1279400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>932800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>626700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>600500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>477600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>778100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>559300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>428700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>452000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>830300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>554300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>697100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>762300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>676000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>524000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>389500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>608900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>492700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>453200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>464500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>440600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>569300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>464400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>516300</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>159000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>596100</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1710100</v>
+      </c>
+      <c r="E33" s="3">
         <v>1805000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2280300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1551300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1513100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1445900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1494500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1344800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1293000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1265300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1282600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1063400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1081000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1237400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>259100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>831500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1192700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1069400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1325300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1028400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1255600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1198400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1194600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>755100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>873200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>290500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>921600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>899000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1130800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1010800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>889100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>902500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1010200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>970300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>971200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>844700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>806700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>795100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1070100</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>704500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1710100</v>
+      </c>
+      <c r="E35" s="3">
         <v>1805000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2280300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1551300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1513100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1445900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1494500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1344800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1293000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1265300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1282600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1063400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1081000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1237400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>259100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>831500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1192700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1069400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1325300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1028400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1255600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1198400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1194600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>755100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>873200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>290500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>921600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>899000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1130800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1010800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>889100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>902500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1010200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>970300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>971200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>844700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>806700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>795100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1070100</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>704500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E38" s="2">
         <v>46142</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45961</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45869</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45777</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45688</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45596</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45504</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45412</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45322</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45230</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45138</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45046</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44957</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44865</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44773</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44592</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44500</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44316</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44227</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44043</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43951</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43861</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43769</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43677</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43585</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43496</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43404</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43312</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43220</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43131</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43039</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42947</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42855</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42766</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,252 +4276,259 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10596800</v>
+      </c>
+      <c r="E41" s="3">
         <v>11997300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7714500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8420300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>13404400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9805200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9010500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5812000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8121900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7113600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6287500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14634100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9939100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>15815100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>16839300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>22981400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>19176800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>15098500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>16909500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>25596500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>22395500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>20216200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>32276500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>33372600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>37849800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>29649800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3732100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2993900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3267300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3216300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3147000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3182900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2757500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3848300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2456600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2560100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>3130900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2777200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2446800</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>2688800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>220085300</v>
+      </c>
+      <c r="E42" s="3">
         <v>225110600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>217347300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>203749200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>201598300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>203433900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>192281500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>190668800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>182408300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>184173500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>168877100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>166358500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>162095500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>147127400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>151898500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>165571400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>133246500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>160608900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>156206100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>155861300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>150134700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>152507200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>147905900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>144551500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>142144300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>147020200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>132310800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>118187100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>124243900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>114917200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>111240500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>99017300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>102777700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>104055200</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>109982300</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>97603900</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>100635800</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>107950900</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>104933300</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>93840800</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4446,41 +4538,41 @@
       <c r="E43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3">
         <v>3289600</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K43" s="3">
         <v>2762100</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N43" s="3">
+      <c r="N43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O43" s="3">
         <v>2577600</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4557,53 +4649,56 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E44" s="3">
+      <c r="D44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3">
         <v>700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>10900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>11600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>11200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>9400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>9900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>11800</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
@@ -4679,8 +4774,11 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4690,42 +4788,42 @@
       <c r="E45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3">
         <v>13410400</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
         <v>7200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>11105100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>117300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4460100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7366800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12095400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8609500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8020700</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>247886800</v>
+      </c>
+      <c r="E46" s="3">
         <v>255866800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>243008400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>245191200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>231077000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>227294400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>214495900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>223329700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>202936300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>206146700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>197686700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>211943400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>191272700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>178902900</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,374 +5024,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>117139200</v>
+      </c>
+      <c r="E47" s="3">
         <v>117706900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>112682700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>110736600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>111042300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>112042800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>106714500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>106988200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>107486300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>101423200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>103078000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>93092300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>95298000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>91635600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>463000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>460600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>462600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>448600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>495800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>487200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>485200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>481300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>494100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>504400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>492200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>482000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>452200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>456900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>484200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>425700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>400300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>382200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>375600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>393700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>413000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>532100</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>550700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>564600</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>545400</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>588500</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2559000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2585900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2528000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2456900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2365700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2371500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2320900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2410500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2360800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2369000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2447100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2340700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2443300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2438600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2439500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2461000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2428300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2440600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2417300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2432800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2320700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2121900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2201500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2297600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2317600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2405400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2423400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1413500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1468200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1374900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1372600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1304400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1304600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1314400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1291200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1326900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1311300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1379700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1345900</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1458100</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5954200</v>
+      </c>
+      <c r="E49" s="3">
         <v>6040200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6055000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5972000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5962600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5943600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5834300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>5936800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>5888500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>5925500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6005000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5880300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>6021700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5900000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5793200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5786400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5592700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5433700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5183600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5169900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5137000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5159900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5275500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5530500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5707600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5997000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5821900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5783600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>6212100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5829100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5754400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5456700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5594000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>5551800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>5348600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>5466200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>5152200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>2307000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2267000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>2265500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>29303500</v>
+      </c>
+      <c r="E52" s="3">
         <v>28106400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>33252500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10836500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>25055800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>27020900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>25503900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7403700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>22159100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>21244200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>20883600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7170500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>20828500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>21450300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>577100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>349800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>235700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>218100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>208700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>297600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>322200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>325100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>389700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>498300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>515200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>430200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>440400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>403100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>451000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>411100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>478100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>436700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>402700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>455400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>451700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>541000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>529900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>540100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>490900</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>592300</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>839551800</v>
+      </c>
+      <c r="E54" s="3">
         <v>852588100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>834981300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>797027200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>796455800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>788918200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>747914400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>747746700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>739437400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>728869300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>726268200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>702501300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>716887500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>689648300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>678686800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>687655700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>662718800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>650054500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>626438300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>620187000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>597086100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>587831800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>587854300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>589968600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>589197300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>595959700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>527646200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>508036100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>532682900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>488149800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>473167600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>433905900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>447928900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>444550300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>436796900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>420675100</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>417436300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>406079500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>394327800</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>385157500</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,53 +6116,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>554118300</v>
+      </c>
+      <c r="E57" s="3">
         <v>554379900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>541537600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>519707000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>516533800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>512632600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>487945200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>499536400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>490116000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>485962600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>492589800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>476712200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>495804300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>484030800</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6109,59 +6239,62 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>63598200</v>
+      </c>
+      <c r="E58" s="3">
         <v>66616000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>168742500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>157571100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>160425600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>157934500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>146504900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>50443500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>138759700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>127286800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>121957000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>48989100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>113851200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>103926700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>68210200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>70914200</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
@@ -6231,8 +6364,11 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6242,42 +6378,42 @@
       <c r="E59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3">
         <v>4145200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3204200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>125200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4466700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7407200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10224800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8620100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8042900</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
-      </c>
       <c r="R59" s="3">
         <v>0</v>
       </c>
@@ -6353,53 +6489,56 @@
       <c r="AP59" s="3">
         <v>0</v>
       </c>
+      <c r="AQ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>617716500</v>
+      </c>
+      <c r="E60" s="3">
         <v>620995900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>710280100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>687896900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>676965200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>670574300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>634457000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>559557200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>629001000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>617716100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>621954000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>541045300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>618275700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>596000300</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,252 +6614,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>147449900</v>
+      </c>
+      <c r="E61" s="3">
         <v>155584000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>51702700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>52797200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>51905800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>51258500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>50893000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>137496200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>48236800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>50055300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>45009700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>114984700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>39706300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>36882700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5754200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4585400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4699200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4573600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4021100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4100900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4187400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4244600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3523800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4379000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4463400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3782400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3685800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3652000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4659300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3210900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3204000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2964900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>12182400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>13819700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>13686800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>12593500</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>11741400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>12597400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>11580300</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>10527800</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26246900</v>
+      </c>
+      <c r="E62" s="3">
         <v>27510600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>24588400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10009400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>22118600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>22220700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>19946700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7983500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>20337600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20576300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>18670400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7832200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>19805200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18750000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>43400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>32800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>76900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>88000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>32000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>28100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>25900</v>
-      </c>
-      <c r="X62" s="3">
-        <v>26300</v>
       </c>
       <c r="Y62" s="3">
         <v>26300</v>
       </c>
       <c r="Z62" s="3">
+        <v>26300</v>
+      </c>
+      <c r="AA62" s="3">
         <v>25300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>26100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>28300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>27500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>29600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>31500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>30800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>31600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>31200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>23300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>24100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>23800</v>
-      </c>
-      <c r="AL62" s="3">
-        <v>22300</v>
       </c>
       <c r="AM62" s="3">
         <v>22300</v>
       </c>
       <c r="AN62" s="3">
+        <v>22300</v>
+      </c>
+      <c r="AO62" s="3">
         <v>15400</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>16900</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>791444000</v>
+      </c>
+      <c r="E66" s="3">
         <v>804126400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>786609500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>751063200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>751023500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>744089000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>705331300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>705402200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>697605900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>688374600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>685662500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>664223700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>677819100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>651667600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>642098400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>651085800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>626782500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>615336900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>592194000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>586391000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>564413500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>555912700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>556504400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>558418300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>558593100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>564503500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>496998700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>478101400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>501321600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>459643400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>445524100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>408513100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>422047200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>419432800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>412881800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>397578600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>395235000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>386360500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>375481600</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>367125600</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,121 +7659,124 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1211800</v>
+      </c>
+      <c r="E70" s="3">
         <v>1248900</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>1251800</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>1212400</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>1227600</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>1446600</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>1277500</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>1540000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>1737500</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>2037300</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>1962000</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>1890000</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>1995600</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>1935700</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>3625300</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>3587700</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>3196100</v>
-      </c>
-      <c r="T70" s="3">
-        <v>3144300</v>
       </c>
       <c r="U70" s="3">
         <v>3144300</v>
       </c>
       <c r="V70" s="3">
+        <v>3144300</v>
+      </c>
+      <c r="W70" s="3">
         <v>3202100</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>2648100</v>
-      </c>
-      <c r="X70" s="3">
-        <v>2684300</v>
       </c>
       <c r="Y70" s="3">
         <v>2684300</v>
       </c>
       <c r="Z70" s="3">
+        <v>2684300</v>
+      </c>
+      <c r="AA70" s="3">
         <v>2740700</v>
       </c>
-      <c r="AA70" s="3">
+      <c r="AB70" s="3">
         <v>2165800</v>
-      </c>
-      <c r="AB70" s="3">
-        <v>2217800</v>
       </c>
       <c r="AC70" s="3">
         <v>2217800</v>
       </c>
       <c r="AD70" s="3">
+        <v>2217800</v>
+      </c>
+      <c r="AE70" s="3">
         <v>2202600</v>
       </c>
-      <c r="AE70" s="3">
+      <c r="AF70" s="3">
         <v>2342100</v>
-      </c>
-      <c r="AF70" s="3">
-        <v>1982300</v>
       </c>
       <c r="AG70" s="3">
         <v>1982300</v>
       </c>
       <c r="AH70" s="3">
+        <v>1982300</v>
+      </c>
+      <c r="AI70" s="3">
         <v>1635100</v>
       </c>
-      <c r="AI70" s="3">
+      <c r="AJ70" s="3">
         <v>1693800</v>
       </c>
-      <c r="AJ70" s="3">
+      <c r="AK70" s="3">
         <v>1692300</v>
       </c>
-      <c r="AK70" s="3">
+      <c r="AL70" s="3">
         <v>1671500</v>
       </c>
-      <c r="AL70" s="3">
+      <c r="AM70" s="3">
         <v>1337300</v>
       </c>
-      <c r="AM70" s="3">
+      <c r="AN70" s="3">
         <v>1336600</v>
-      </c>
-      <c r="AN70" s="3">
-        <v>768200</v>
       </c>
       <c r="AO70" s="3">
         <v>768200</v>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>768200</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>768200</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>27355400</v>
+      </c>
+      <c r="E72" s="3">
         <v>28037300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>27714300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>26025100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>25763200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>25317300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>23744700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>24019400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>23777100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>23275600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>23291900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>21853600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>22651500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>21561700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>20907700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>21005000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>21016100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>20041500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>19489000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>19096100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>18559200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>18022900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>17314800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>16957300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>16656000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>16672900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>16912300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>16351200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>17024500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>15237000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>14704300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>13470700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>13588600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>13107600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>12429100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>11982500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>11561300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>11531900</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>11126300</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>10435600</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>46685700</v>
+      </c>
+      <c r="E76" s="3">
         <v>46999000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>46906900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>44548900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>44004500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>43180000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>41105900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>40609300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>39910100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>38277800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>38468000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>36220600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>36908600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>35886500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>32963000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>32982200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>32740200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>31573300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>31100000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>30593900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>30024400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>29234700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>28665600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>28809600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>28438500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>29238400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>28429800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>27732100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>29019200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>26524100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>25661200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>23757700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>24187900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>23425300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>22243700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>21759200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>20864700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>18950700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>18078000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>17263700</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46234</v>
+      </c>
+      <c r="E80" s="2">
         <v>46142</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45961</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45869</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45777</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45688</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45596</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45504</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45412</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45322</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45230</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45138</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45046</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44957</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44865</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44773</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44592</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44500</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44316</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44227</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44043</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43951</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43861</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43769</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43677</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43585</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43496</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43404</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43312</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43220</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43131</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43039</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42947</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42855</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42766</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1710100</v>
+      </c>
+      <c r="E81" s="3">
         <v>1805000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2280300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1551300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1513100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1445900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1494500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1344800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1293000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1265300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1282600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1063400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1081000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1237400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>259100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>831500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1192700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1069400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1325300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1028400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1255600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1198400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1194600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>755100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>873200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>290500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>921600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>899000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1130800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1010800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>889100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>902500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1010200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>970300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>971200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>844700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>806700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>795100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1070100</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>704500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>199400</v>
+      </c>
+      <c r="E83" s="3">
         <v>203400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>192800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>207400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>223700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>199400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>195100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>223200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>190800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>188000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>188200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>203900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>181800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>181000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>203900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>202600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>192100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>186100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>183900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>212500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>180700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>187000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>178000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>242300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>190900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>197800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>193100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>243300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>146700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>137000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>131600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>117700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>125700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>122000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>123500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>113100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>106400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>97600</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>92200</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>99100</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-9976000</v>
+      </c>
+      <c r="E89" s="3">
         <v>514200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6373400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-12442700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>103300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-744700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3469900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-15047700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2002400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3947900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>186900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3894500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3566900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2338300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>103800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>6460500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5873500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4998200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-707400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>6147900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5358500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-13250400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-918300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-2295300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>14240300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>34572800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>529900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4656200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2110800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3311000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4477300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-880700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1409200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>4979000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1929700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1486900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1329900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>2179500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-3199700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1977400</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,116 +9881,117 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-215300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-235100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-181400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-276900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-203800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-178000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-133400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-282000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-199100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-154200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-156200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-208800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-180900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-177000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-246000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-392000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-272000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-244000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-201000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-270000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-210000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-216200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-53300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-76700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-75100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-38500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-48700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-82600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-44800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-43900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-42300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-95900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-28600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-33900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-29800</v>
       </c>
-      <c r="AL91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM91" s="3" t="s">
         <v>5</v>
       </c>
@@ -9781,11 +10001,14 @@
       <c r="AO91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AP91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ91" s="3">
         <v>-57600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3005300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5445100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1462700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-512400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>752200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-428400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3804300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-762800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6763800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1210700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6488600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3132700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-915300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4463500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6739100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2357500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1452100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-6998200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6953900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2954800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2457800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>1006200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>1849400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2178800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5510600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-8162200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>800000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3415000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3258200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2834500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4539600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>1944600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1535700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-4410600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-2057000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1830800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1102900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1667800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>3186600</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-1363600</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,8 +10426,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10238,86 +10471,89 @@
       <c r="P96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R96" s="3">
         <v>-367300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-519600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-458900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-535100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-531400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-496000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-485200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-505300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-488800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-498300</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-492200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-504800</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-499300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-485700</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-507400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-463400</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-438000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-420800</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-426100</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-428300</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-294000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>115400</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-416800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-397900</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-385700</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-374900</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,370 +10924,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>11879900</v>
+      </c>
+      <c r="E100" s="3">
         <v>9193200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3952300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>8127700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2802100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1608700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>10626600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>13547900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>5755300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6127800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2536800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>12173100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1836700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>6076200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>290800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-146500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-584500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>167200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-616500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>34800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-478500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>256000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1266700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>6900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>244600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-594300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-621800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1317600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>973300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-436500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-159400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-559600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-996700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>737000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>90800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-275400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>323000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-242800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-191300</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-218200</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-87600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>78100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>24400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>41500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-60500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>89300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-63900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>36100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-30000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>114400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-7800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>23400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-29400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>113700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-7400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>21800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>52300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-15500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>29600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-72100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-73600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-79000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>101300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>9400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-22400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>29300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>16700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>32400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>58000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-67000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>48400</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-109400</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>61500</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-37600</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>33000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1042100</v>
+      </c>
+      <c r="E102" s="3">
         <v>4255000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1018900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4796700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3677900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>348100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3430500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2238200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1002700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1010600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8899100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5235200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6382800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-689500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6374000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4070100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3829400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1811000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-8225400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3212400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2451800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-12060300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-409200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-4477200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>8895300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>25917600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>717500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-78700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-196500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>69300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-224800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>521000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1090800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1363300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-103400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-570800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>440600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>330300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-242000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>428700</v>
       </c>
     </row>
